--- a/artfynd/A 15371-2025 artfynd.xlsx
+++ b/artfynd/A 15371-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>5956888</v>
       </c>
       <c r="B2" t="n">
-        <v>96253</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98491</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465228.1045374677</v>
+        <v>465228</v>
       </c>
       <c r="R2" t="n">
-        <v>6533172.526043469</v>
+        <v>6533173</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -744,19 +739,9 @@
           <t>1991-08-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1991-08-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -795,12 +780,7 @@
         <v>2845133</v>
       </c>
       <c r="B3" t="n">
-        <v>96366</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465228.1045374677</v>
+        <v>465228</v>
       </c>
       <c r="R3" t="n">
-        <v>6533172.526043469</v>
+        <v>6533173</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -865,19 +845,9 @@
           <t>1991-08-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1991-08-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 15371-2025 artfynd.xlsx
+++ b/artfynd/A 15371-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5956888</v>
       </c>
       <c r="B2" t="n">
-        <v>98491</v>
+        <v>98499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>2845133</v>
       </c>
       <c r="B3" t="n">
-        <v>98605</v>
+        <v>98613</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15371-2025 artfynd.xlsx
+++ b/artfynd/A 15371-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5956888</v>
       </c>
       <c r="B2" t="n">
-        <v>98499</v>
+        <v>98505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>2845133</v>
       </c>
       <c r="B3" t="n">
-        <v>98613</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15371-2025 artfynd.xlsx
+++ b/artfynd/A 15371-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5956888</v>
       </c>
       <c r="B2" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>2845133</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15371-2025 artfynd.xlsx
+++ b/artfynd/A 15371-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5956888</v>
       </c>
       <c r="B2" t="n">
-        <v>98508</v>
+        <v>98511</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>2845133</v>
       </c>
       <c r="B3" t="n">
-        <v>98622</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15371-2025 artfynd.xlsx
+++ b/artfynd/A 15371-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5956888</v>
       </c>
       <c r="B2" t="n">
-        <v>98511</v>
+        <v>98512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>2845133</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98626</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15371-2025 artfynd.xlsx
+++ b/artfynd/A 15371-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5956888</v>
       </c>
       <c r="B2" t="n">
-        <v>98512</v>
+        <v>98539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>2845133</v>
       </c>
       <c r="B3" t="n">
-        <v>98626</v>
+        <v>98653</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15371-2025 artfynd.xlsx
+++ b/artfynd/A 15371-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5956888</v>
       </c>
       <c r="B2" t="n">
-        <v>98539</v>
+        <v>98545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>2845133</v>
       </c>
       <c r="B3" t="n">
-        <v>98653</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15371-2025 artfynd.xlsx
+++ b/artfynd/A 15371-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5956888</v>
       </c>
       <c r="B2" t="n">
-        <v>98545</v>
+        <v>98552</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>2845133</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15371-2025 artfynd.xlsx
+++ b/artfynd/A 15371-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5956888</v>
       </c>
       <c r="B2" t="n">
-        <v>98552</v>
+        <v>98556</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>2845133</v>
       </c>
       <c r="B3" t="n">
-        <v>98666</v>
+        <v>98670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15371-2025 artfynd.xlsx
+++ b/artfynd/A 15371-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>5956888</v>
       </c>
       <c r="B2" t="n">
-        <v>98556</v>
+        <v>98563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>2845133</v>
       </c>
       <c r="B3" t="n">
-        <v>98670</v>
+        <v>98677</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
